--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלו חנן - כל הדרך הביתה קאבר</v>
+        <v>שלמה דעוס - צעקתי בלילה קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409858&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409894&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלו חנן - כל הדרך הביתה קאבר</v>
+        <v>שלמה דעוס - צעקתי בלילה קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עילאי גניש - שכחת את הכל קאבר</v>
+        <v>נועם דדון - בכה כינור קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-06</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409857&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409893&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עילאי גניש - שכחת את הכל קאבר</v>
+        <v>נועם דדון - בכה כינור קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נועם דדון - שירו של צנחן קאבר</v>
+        <v>ליאור כהן - סיפור ישן קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-06</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409856&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409892&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נועם דדון - שירו של צנחן קאבר</v>
+        <v>ליאור כהן - סיפור ישן קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מושיק עפיה - נתתי לך ת'לב קאבר</v>
+        <v>ליאור כהן - לב שבור לרסיסים קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-06</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409855&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409891&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מושיק עפיה - נתתי לך ת'לב קאבר</v>
+        <v>ליאור כהן - לב שבור לרסיסים קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליאור כהן - קרב בשדה האהבה קאבר</v>
+        <v>ליאור כהן - חלון לים התיכון קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-06</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409854&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409890&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליאור כהן - קרב בשדה האהבה קאבר</v>
+        <v>ליאור כהן - חלון לים התיכון קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ליאור כהן - לילד הזה התפללתי קאבר</v>
+        <v>דניאל סעדון - באתי לגני קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-06</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409853&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409889&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,88 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ליאור כהן - לילד הזה התפללתי קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ליאור כהן - הצייר קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409852&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>ליאור כהן - הצייר קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>יונתן אברהם - מכאן ועד הנצח קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409851&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>יונתן אברהם - מכאן ועד הנצח קאבר</v>
+        <v>דניאל סעדון - באתי לגני קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>